--- a/resources/topic/银行从业中级个人贷款_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业中级个人贷款_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R673af707d0c548a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R36adacd5ddb64398"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R254fe2946d2c4fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R1f4c1b50d1d946db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R705d6bdc74fc4024"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R6ded492679814f20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -56735,7 +56735,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 09:12:47+08:00（本地时间）</x:v>
+        <x:v>2026-09-10 15:10:11+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">

--- a/resources/topic/银行从业中级个人贷款_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业中级个人贷款_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R1f4c1b50d1d946db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R705d6bdc74fc4024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R6ded492679814f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rcd6967e69a844405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Rd0f088e9bcf34f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rff981e1aec8645b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -56735,7 +56735,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 15:10:11+08:00（本地时间）</x:v>
+        <x:v>2026-09-12 01:04:42+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
